--- a/results/Int Task Remove ACC 0.2/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.2/Linea_fi_explain.xlsx
@@ -1166,13 +1166,13 @@
         <v>0.0404486178409518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005887803035742116</v>
+        <v>0.005896046025820343</v>
       </c>
       <c r="I3" t="n">
         <v>-0.0002903828695281352</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02921330653803599</v>
+        <v>0.02921323026200538</v>
       </c>
       <c r="K3" t="n">
         <v>0.01718935283069287</v>
@@ -1184,7 +1184,7 @@
         <v>0.006260392529667315</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04927227624796163</v>
+        <v>0.04927177514255422</v>
       </c>
       <c r="O3" t="n">
         <v>0.01532359991125629</v>
@@ -1196,7 +1196,7 @@
         <v>0.01233291847266342</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01670583618584319</v>
+        <v>0.0167055796960985</v>
       </c>
       <c r="S3" t="n">
         <v>0.3311316477957636</v>
@@ -1208,7 +1208,7 @@
         <v>0.1629994273044344</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0002901368314740316</v>
+        <v>-0.0002984128063173352</v>
       </c>
       <c r="W3" t="n">
         <v>0.01278597557591365</v>
@@ -1232,7 +1232,7 @@
         <v>0.06282972230413345</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.160577406284037</v>
+        <v>0.1605733626123832</v>
       </c>
       <c r="AE3" t="n">
         <v>0.2694315532192637</v>
@@ -1316,7 +1316,7 @@
         <v>0.000282729519239907</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.02626648072980627</v>
+        <v>0.02626256530302475</v>
       </c>
       <c r="BG3" t="n">
         <v>0.0158070825061503</v>
@@ -1355,7 +1355,7 @@
         <v>0.001922416557262401</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0004036687078684188</v>
+        <v>-0.0004068315339681583</v>
       </c>
       <c r="BT3" t="n">
         <v>0.001356695298023972</v>
@@ -1364,10 +1364,10 @@
         <v>0.04088065654623472</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001310443922624178</v>
+        <v>-0.001306575450670601</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.005135530795755259</v>
+        <v>0.005131343191065141</v>
       </c>
       <c r="BX3" t="n">
         <v>-8.461922776460074e-05</v>
@@ -1385,7 +1385,7 @@
         <v>-8.755809453068196e-06</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.000375282365625057</v>
+        <v>-0.0003711209007894356</v>
       </c>
       <c r="CD3" t="n">
         <v>0.001309349441201354</v>
@@ -1437,13 +1437,13 @@
         <v>0.03875428862087028</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008080976999496692</v>
+        <v>0.008087467606133606</v>
       </c>
       <c r="I4" t="n">
         <v>0.001413728119113377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02352480823902042</v>
+        <v>0.02353822342035465</v>
       </c>
       <c r="K4" t="n">
         <v>0.01643668384350273</v>
@@ -1455,7 +1455,7 @@
         <v>0.01781261377249188</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03803171905062131</v>
+        <v>0.03802602670309514</v>
       </c>
       <c r="O4" t="n">
         <v>0.02239278838856402</v>
@@ -1467,7 +1467,7 @@
         <v>0.01580902133968567</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01370611693613573</v>
+        <v>0.01370397284106356</v>
       </c>
       <c r="S4" t="n">
         <v>0.09315057126830595</v>
@@ -1479,7 +1479,7 @@
         <v>0.07890172714975437</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001400800432169008</v>
+        <v>0.001419901446030242</v>
       </c>
       <c r="W4" t="n">
         <v>0.01164308455927232</v>
@@ -1503,7 +1503,7 @@
         <v>0.0562069478177142</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0904215844604126</v>
+        <v>0.09042424976948313</v>
       </c>
       <c r="AE4" t="n">
         <v>0.091125093511863</v>
@@ -1587,7 +1587,7 @@
         <v>0.001730344509469667</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.03925734962097379</v>
+        <v>0.03926113003614917</v>
       </c>
       <c r="BG4" t="n">
         <v>0.03968599332646024</v>
@@ -1626,7 +1626,7 @@
         <v>0.01907825184211528</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004781063322032353</v>
+        <v>0.004798103440894584</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002193645524013048</v>
@@ -1635,10 +1635,10 @@
         <v>0.03473603314357774</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02300547546334438</v>
+        <v>0.02299764156022117</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.02679627349679957</v>
+        <v>0.02679731390699369</v>
       </c>
       <c r="BX4" t="n">
         <v>0.0006171111415772005</v>
@@ -1656,7 +1656,7 @@
         <v>0.0003733224850867806</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.00456301868549315</v>
+        <v>0.004557933087569253</v>
       </c>
       <c r="CD4" t="n">
         <v>0.00802165177914967</v>
@@ -1726,7 +1726,7 @@
         <v>-0.01856013316687473</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.00931871574001567</v>
+        <v>-0.009279561472200482</v>
       </c>
       <c r="O5" t="n">
         <v>-0.01096319498825373</v>
@@ -1750,7 +1750,7 @@
         <v>0.04926029588164734</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.002954640033291722</v>
+        <v>-0.003037869330004161</v>
       </c>
       <c r="W5" t="n">
         <v>-0.006783919597989918</v>
@@ -1858,7 +1858,7 @@
         <v>-0.002623335943617866</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.007830853563038387</v>
+        <v>-0.007870007830853575</v>
       </c>
       <c r="BG5" t="n">
         <v>-0.02789716039907903</v>
@@ -1897,7 +1897,7 @@
         <v>-0.02154738878143139</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.008557175748273183</v>
+        <v>-0.008672294704527983</v>
       </c>
       <c r="BT5" t="n">
         <v>-0.001283048211508553</v>
@@ -1906,7 +1906,7 @@
         <v>-0.01905360134003349</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.04324951644100587</v>
+        <v>-0.04321083172147009</v>
       </c>
       <c r="BW5" t="n">
         <v>-0.05647969052224376</v>
@@ -2009,7 +2009,7 @@
         <v>0.00137800024666771</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004342104191995872</v>
+        <v>0.004361681325903468</v>
       </c>
       <c r="S6" t="n">
         <v>0.2744351713418959</v>
@@ -2045,7 +2045,7 @@
         <v>0.02228491355820621</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1015919503068536</v>
+        <v>0.1015818411277189</v>
       </c>
       <c r="AE6" t="n">
         <v>0.2287260893544526</v>
@@ -2168,7 +2168,7 @@
         <v>-0.008327452193789258</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.003412545302865139</v>
+        <v>-0.003402076291139844</v>
       </c>
       <c r="BT6" t="n">
         <v>7.349935291753871e-05</v>
@@ -2180,7 +2180,7 @@
         <v>-0.01379511628817029</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.0005503802058503842</v>
+        <v>-0.0005817872410262687</v>
       </c>
       <c r="BX6" t="n">
         <v>-0.0002692697392460558</v>
@@ -2250,13 +2250,13 @@
         <v>0.0338800553852359</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004207828620243997</v>
+        <v>0.0041883884958272</v>
       </c>
       <c r="I7" t="n">
         <v>0.0003350610053479474</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02771889208089529</v>
+        <v>0.0276995497211274</v>
       </c>
       <c r="K7" t="n">
         <v>0.01765098056368236</v>
@@ -2268,7 +2268,7 @@
         <v>0.008530383580654517</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05443085066320092</v>
+        <v>0.0544087680022563</v>
       </c>
       <c r="O7" t="n">
         <v>0.00802852265003795</v>
@@ -2280,7 +2280,7 @@
         <v>0.00615181877981404</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01919922422330004</v>
+        <v>0.01915878750676143</v>
       </c>
       <c r="S7" t="n">
         <v>0.357349262430787</v>
@@ -2521,13 +2521,13 @@
         <v>0.06581412425921308</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01308296722592388</v>
+        <v>0.01311329476332784</v>
       </c>
       <c r="I8" t="n">
         <v>0.0006945229645085732</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04225376271902753</v>
+        <v>0.04228483148456191</v>
       </c>
       <c r="K8" t="n">
         <v>0.02592936188047144</v>
@@ -2563,7 +2563,7 @@
         <v>0.2165004070388882</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0006945229645085732</v>
+        <v>0.0006848517846246265</v>
       </c>
       <c r="W8" t="n">
         <v>0.02230722541523557</v>
@@ -2798,7 +2798,7 @@
         <v>0.001118475559237741</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06822716807367615</v>
+        <v>0.06826554105909441</v>
       </c>
       <c r="K9" t="n">
         <v>0.04271730618637428</v>
